--- a/ConfigTools/Config/Datas/Monster.xlsx
+++ b/ConfigTools/Config/Datas/Monster.xlsx
@@ -1088,7 +1088,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="10" width="13.6363636363636" customWidth="1"/>
@@ -1341,6 +1341,111 @@
         <v>0</v>
       </c>
       <c r="H12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="7">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7">
+        <v>100</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14" s="7">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7">
+        <v>100</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15" s="7">
+        <v>10</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7">
+        <v>100</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16" s="7">
+        <v>11</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7">
+        <v>100</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="7">
+        <v>12</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7">
+        <v>300</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
         <v>0</v>
       </c>
     </row>
